--- a/data/trans_orig/P16A15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29812</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>43076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254887</t>
+          <t>254622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267054</t>
+          <t>267402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231026</t>
+          <t>229709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247989</t>
+          <t>247766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>490216</t>
+          <t>490772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512056</t>
+          <t>512281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44494</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>88575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448581</t>
+          <t>448568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471153</t>
+          <t>470412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>452942</t>
+          <t>453326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475444</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908790</t>
+          <t>908449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940543</t>
+          <t>940133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35670</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t>38713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67641</t>
+          <t>67319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283176</t>
+          <t>283079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301720</t>
+          <t>302369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294464</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316601</t>
+          <t>316569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586617</t>
+          <t>586939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614147</t>
+          <t>613726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333590</t>
+          <t>333493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348950</t>
+          <t>348808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342942</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359673</t>
+          <t>359340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682531</t>
+          <t>682848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>704739</t>
+          <t>704829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177754</t>
+          <t>179917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186978</t>
+          <t>186318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201122</t>
+          <t>200783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372450</t>
+          <t>372121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393415</t>
+          <t>392534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41953</t>
+          <t>42244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>58780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249363</t>
+          <t>248398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264003</t>
+          <t>263190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236191</t>
+          <t>235900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256521</t>
+          <t>256557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491104</t>
+          <t>490175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514904</t>
+          <t>516270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49362</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64234</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102873</t>
+          <t>101772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565665</t>
+          <t>568334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590037</t>
+          <t>590307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>573985</t>
+          <t>574394</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>601126</t>
+          <t>601947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1150373</t>
+          <t>1151474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1185720</t>
+          <t>1187348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>57167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52909</t>
+          <t>53411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>86525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93043</t>
+          <t>90922</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131480</t>
+          <t>131439</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684678</t>
+          <t>685610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710919</t>
+          <t>710881</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>697630</t>
+          <t>696986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>730602</t>
+          <t>730100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1394808</t>
+          <t>1394849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1433245</t>
+          <t>1435366</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>164412</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>217366</t>
+          <t>218178</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297241</t>
+          <t>297745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>413344</t>
+          <t>420869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>500464</t>
+          <t>502330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3058159</t>
+          <t>3057347</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3111113</t>
+          <t>3111185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3081956</t>
+          <t>3081452</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3141086</t>
+          <t>3143202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6154258</t>
+          <t>6152392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6241378</t>
+          <t>6233853</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>38732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41026</t>
+          <t>40989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>72941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253405</t>
+          <t>254277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275568</t>
+          <t>276004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241727</t>
+          <t>241535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263215</t>
+          <t>263004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501365</t>
+          <t>501399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533314</t>
+          <t>533351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>48709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80780</t>
+          <t>81552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,82 +4414,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>77738</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>61989</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>96346</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>118428</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>164365</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>15,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77738</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61389</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>95598</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>140333</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>118176</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>164449</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424747</t>
+          <t>423975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457977</t>
+          <t>456818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,82 +4527,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>83,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>444993</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>426385</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>460742</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>887925</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>863893</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>909830</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>86,35%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>84,02%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>444993</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427133</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>461342</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,13%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>88,26%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>828</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>887925</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>863809</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>910082</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>45422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59595</t>
+          <t>61123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93148</t>
+          <t>94402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278091</t>
+          <t>277694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299721</t>
+          <t>299268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>285585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310801</t>
+          <t>310768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>570988</t>
+          <t>569734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604541</t>
+          <t>603013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>53195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>40584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>66084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109154</t>
+          <t>112255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>321085</t>
+          <t>320787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346605</t>
+          <t>347008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321578</t>
+          <t>321890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348732</t>
+          <t>347390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>652802</t>
+          <t>649701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>689499</t>
+          <t>687123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53791</t>
+          <t>54008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>58263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86831</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172223</t>
+          <t>171701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192851</t>
+          <t>192186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165800</t>
+          <t>165583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190166</t>
+          <t>188541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345378</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376653</t>
+          <t>373946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47801</t>
+          <t>47840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26569</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48597</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89410</t>
+          <t>91129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226180</t>
+          <t>226141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248256</t>
+          <t>248609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230543</t>
+          <t>230484</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252571</t>
+          <t>252303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463711</t>
+          <t>461992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497398</t>
+          <t>494981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88034</t>
+          <t>88402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>59728</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94462</t>
+          <t>94784</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120458</t>
+          <t>121876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169403</t>
+          <t>171436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573942</t>
+          <t>573574</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607928</t>
+          <t>606501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>598311</t>
+          <t>597989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>633838</t>
+          <t>633045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1185345</t>
+          <t>1183312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1234290</t>
+          <t>1232872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70924</t>
+          <t>72540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66905</t>
+          <t>66806</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103796</t>
+          <t>102243</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115113</t>
+          <t>116554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162003</t>
+          <t>163524</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>706048</t>
+          <t>704432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>736622</t>
+          <t>735628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>717724</t>
+          <t>719277</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>754615</t>
+          <t>754714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1436489</t>
+          <t>1434968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1483379</t>
+          <t>1481938</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>311936</t>
+          <t>315960</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>386535</t>
+          <t>387073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,82 +6815,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>435567</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>397571</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>482700</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>787555</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>731552</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>845405</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>435567</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>395711</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>474950</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>787555</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>734156</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>840868</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3034646</t>
+          <t>3034108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3109245</t>
+          <t>3105221</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,82 +6928,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3110513</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3063380</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3148509</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6179706</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6121856</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6235709</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>88,7%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3110513</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3071130</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3150369</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6179706</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6126393</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6233105</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>39208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63491</t>
+          <t>62356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263220</t>
+          <t>263606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280729</t>
+          <t>280965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249503</t>
+          <t>249495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269299</t>
+          <t>269968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518973</t>
+          <t>520108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546131</t>
+          <t>547338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>66558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>85945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98224</t>
+          <t>99633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143976</t>
+          <t>143968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434144</t>
+          <t>436017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463594</t>
+          <t>464230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439139</t>
+          <t>437139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470689</t>
+          <t>469945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881683</t>
+          <t>881691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927435</t>
+          <t>926026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50298</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>59387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66834</t>
+          <t>66575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101339</t>
+          <t>99874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268267</t>
+          <t>268302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290459</t>
+          <t>290868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276807</t>
+          <t>276922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304616</t>
+          <t>302729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553535</t>
+          <t>555000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588040</t>
+          <t>588299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28472</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52218</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>66782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73863</t>
+          <t>72543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>109847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317746</t>
+          <t>317003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341492</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320858</t>
+          <t>320501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349274</t>
+          <t>348708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>648206</t>
+          <t>647400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683384</t>
+          <t>684704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40653</t>
+          <t>40873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>72521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174848</t>
+          <t>175941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193288</t>
+          <t>194776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177934</t>
+          <t>177714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197724</t>
+          <t>197458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359322</t>
+          <t>357287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388273</t>
+          <t>386997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36038</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>62071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229556</t>
+          <t>229671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247798</t>
+          <t>247450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236697</t>
+          <t>237080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255888</t>
+          <t>256696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473624</t>
+          <t>474167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500200</t>
+          <t>500527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37945</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67827</t>
+          <t>68701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68572</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87955</t>
+          <t>87195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129341</t>
+          <t>127701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>588731</t>
+          <t>587857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>618613</t>
+          <t>616348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>622722</t>
+          <t>618623</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650824</t>
+          <t>650258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1218511</t>
+          <t>1220151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1259897</t>
+          <t>1260657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53290</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86285</t>
+          <t>85227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72419</t>
+          <t>73474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111119</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137432</t>
+          <t>133731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185004</t>
+          <t>184748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692298</t>
+          <t>693356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>725293</t>
+          <t>724982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>715048</t>
+          <t>713581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>753748</t>
+          <t>752693</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419746</t>
+          <t>1420002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1467318</t>
+          <t>1471019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>283875</t>
+          <t>288562</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>351976</t>
+          <t>356536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351406</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>430726</t>
+          <t>426247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>655378</t>
+          <t>655952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>761595</t>
+          <t>761295</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3042374</t>
+          <t>3037814</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3110475</t>
+          <t>3105788</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3113816</t>
+          <t>3118295</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3193136</t>
+          <t>3195707</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6177297</t>
+          <t>6177597</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6283514</t>
+          <t>6282940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51255</t>
+          <t>49866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>63080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89882</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260188</t>
+          <t>261577</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282760</t>
+          <t>282809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243267</t>
+          <t>242415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259182</t>
+          <t>259670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511195</t>
+          <t>510646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538140</t>
+          <t>537997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65609</t>
+          <t>64451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>51465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74232</t>
+          <t>75228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94635</t>
+          <t>93256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132036</t>
+          <t>128918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>451784</t>
+          <t>452942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481379</t>
+          <t>481492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439493</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463501</t>
+          <t>462260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>899082</t>
+          <t>902200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>936483</t>
+          <t>937862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>36977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117963</t>
+          <t>119295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256791</t>
+          <t>256752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278577</t>
+          <t>279073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283731</t>
+          <t>283874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303863</t>
+          <t>305174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547215</t>
+          <t>545883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578134</t>
+          <t>575999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66816</t>
+          <t>68890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67327</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108323</t>
+          <t>109258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262149</t>
+          <t>262490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>285463</t>
+          <t>285549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408902</t>
+          <t>406828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>445863</t>
+          <t>444185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679951</t>
+          <t>679016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720947</t>
+          <t>724145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53096</t>
+          <t>53253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64933</t>
+          <t>65661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86396</t>
+          <t>87110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141168</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156346</t>
+          <t>155695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155560</t>
+          <t>155403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>170265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301002</t>
+          <t>300288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322465</t>
+          <t>321737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46914</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68414</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>36138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85311</t>
+          <t>87196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>113103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201222</t>
+          <t>201187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222722</t>
+          <t>222532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204295</t>
+          <t>204654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221110</t>
+          <t>220918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413409</t>
+          <t>413589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441381</t>
+          <t>439496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80746</t>
+          <t>81525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115400</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>537503</t>
+          <t>575411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174948</t>
+          <t>173702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>794325</t>
+          <t>761311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>543533</t>
+          <t>542754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571445</t>
+          <t>572076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311762</t>
+          <t>273854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>733865</t>
+          <t>735455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>679219</t>
+          <t>712233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1298596</t>
+          <t>1299842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>33349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103742</t>
+          <t>103480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100021</t>
+          <t>100757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93445</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195072</t>
+          <t>192930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>824978</t>
+          <t>825240</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>898201</t>
+          <t>895371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>614830</t>
+          <t>614094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641289</t>
+          <t>641945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1448500</t>
+          <t>1450642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1550127</t>
+          <t>1549903</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>310253</t>
+          <t>294988</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>443635</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>491218</t>
+          <t>486816</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1258568</t>
+          <t>1202240</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>874918</t>
+          <t>867714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1732706</t>
+          <t>1724811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3015185</t>
+          <t>3015988</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3148567</t>
+          <t>3163832</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2399465</t>
+          <t>2455793</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3166815</t>
+          <t>3171217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5384147</t>
+          <t>5392042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6241935</t>
+          <t>6249139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254622</t>
+          <t>254980</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267402</t>
+          <t>267396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229709</t>
+          <t>229350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247766</t>
+          <t>247382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>490772</t>
+          <t>489955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512281</t>
+          <t>511919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22663</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>43585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>56138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448568</t>
+          <t>449490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470412</t>
+          <t>471562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453326</t>
+          <t>452329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>475515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908449</t>
+          <t>908474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940133</t>
+          <t>940886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38713</t>
+          <t>38451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67319</t>
+          <t>65906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283079</t>
+          <t>284148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302369</t>
+          <t>301979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296699</t>
+          <t>296961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316569</t>
+          <t>316824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586939</t>
+          <t>588352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613726</t>
+          <t>616036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>47743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333493</t>
+          <t>334070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348808</t>
+          <t>349451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343341</t>
+          <t>341916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359340</t>
+          <t>359110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682848</t>
+          <t>682384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>704829</t>
+          <t>704500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23391</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179917</t>
+          <t>177896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195522</t>
+          <t>194744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186318</t>
+          <t>186869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200783</t>
+          <t>201351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372121</t>
+          <t>372340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392534</t>
+          <t>393013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42244</t>
+          <t>43324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58780</t>
+          <t>58813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248398</t>
+          <t>248072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263190</t>
+          <t>263154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235900</t>
+          <t>234820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256557</t>
+          <t>256302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490175</t>
+          <t>490142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516270</t>
+          <t>515699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46693</t>
+          <t>47415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63825</t>
+          <t>64623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101772</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>568334</t>
+          <t>567612</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590307</t>
+          <t>590372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574394</t>
+          <t>573596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>601947</t>
+          <t>602119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1151474</t>
+          <t>1150561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1187348</t>
+          <t>1184648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57167</t>
+          <t>56393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53411</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86525</t>
+          <t>86650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90922</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131439</t>
+          <t>132570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685610</t>
+          <t>686384</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710881</t>
+          <t>710395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696986</t>
+          <t>696861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>730100</t>
+          <t>730069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1394849</t>
+          <t>1393718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1435366</t>
+          <t>1433685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>164340</t>
+          <t>164565</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>218178</t>
+          <t>216536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>236389</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297745</t>
+          <t>297601</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>420869</t>
+          <t>419808</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>502330</t>
+          <t>496259</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3057347</t>
+          <t>3058989</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3111185</t>
+          <t>3110960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3081452</t>
+          <t>3081596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3143202</t>
+          <t>3142808</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6152392</t>
+          <t>6158463</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6233853</t>
+          <t>6234914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38732</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40989</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72941</t>
+          <t>67460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254277</t>
+          <t>255442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276004</t>
+          <t>276998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241535</t>
+          <t>241394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263004</t>
+          <t>262752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501399</t>
+          <t>506880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533351</t>
+          <t>535519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81552</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61989</t>
+          <t>62805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96346</t>
+          <t>96274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118428</t>
+          <t>119542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164365</t>
+          <t>168221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423975</t>
+          <t>424244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456818</t>
+          <t>457409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426385</t>
+          <t>426457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460742</t>
+          <t>459926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>863893</t>
+          <t>860037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>909830</t>
+          <t>908716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61123</t>
+          <t>59832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94402</t>
+          <t>91969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277694</t>
+          <t>276520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299268</t>
+          <t>299116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285585</t>
+          <t>284764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310768</t>
+          <t>310641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569734</t>
+          <t>572167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>603013</t>
+          <t>604304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53195</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40584</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66084</t>
+          <t>67248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74833</t>
+          <t>74870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112255</t>
+          <t>112587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320787</t>
+          <t>320260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347008</t>
+          <t>346872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321890</t>
+          <t>320726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347390</t>
+          <t>347714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649701</t>
+          <t>649369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>687123</t>
+          <t>687086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>40956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31050</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>53414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171701</t>
+          <t>171662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192186</t>
+          <t>192887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165583</t>
+          <t>166177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188541</t>
+          <t>189824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>344008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373946</t>
+          <t>376990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48656</t>
+          <t>50364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91129</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226141</t>
+          <t>227054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248609</t>
+          <t>248632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230484</t>
+          <t>228776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252303</t>
+          <t>251484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461992</t>
+          <t>462873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494981</t>
+          <t>495390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88402</t>
+          <t>88345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94784</t>
+          <t>93599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121876</t>
+          <t>122817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171436</t>
+          <t>169553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573574</t>
+          <t>573631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>606501</t>
+          <t>607064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>597989</t>
+          <t>599174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>633045</t>
+          <t>633929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1183312</t>
+          <t>1185195</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1232872</t>
+          <t>1231931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>40693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72540</t>
+          <t>72009</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66806</t>
+          <t>65622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102243</t>
+          <t>102254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116554</t>
+          <t>115645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163524</t>
+          <t>159874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>704432</t>
+          <t>704963</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>735628</t>
+          <t>736279</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719277</t>
+          <t>719266</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>754714</t>
+          <t>755898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1434968</t>
+          <t>1438618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1481938</t>
+          <t>1482847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>315960</t>
+          <t>318298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>387073</t>
+          <t>393069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>397571</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>482700</t>
+          <t>475543</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>731552</t>
+          <t>738161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>845405</t>
+          <t>841006</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3034108</t>
+          <t>3028112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3105221</t>
+          <t>3102883</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3063380</t>
+          <t>3070537</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3148509</t>
+          <t>3148444</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6121856</t>
+          <t>6126255</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6235709</t>
+          <t>6229100</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39208</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62356</t>
+          <t>65070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263606</t>
+          <t>262665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280965</t>
+          <t>281121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249495</t>
+          <t>247557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269968</t>
+          <t>269272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520108</t>
+          <t>517394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>547338</t>
+          <t>545998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66558</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53139</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85945</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99633</t>
+          <t>100486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143968</t>
+          <t>143131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436017</t>
+          <t>436533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>464230</t>
+          <t>463372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>437139</t>
+          <t>439403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469945</t>
+          <t>470637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881691</t>
+          <t>882528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926026</t>
+          <t>925173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>28609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>49730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59387</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>66932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268302</t>
+          <t>268835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290868</t>
+          <t>289956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276922</t>
+          <t>277207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302729</t>
+          <t>303006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555000</t>
+          <t>553168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588299</t>
+          <t>587942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52961</t>
+          <t>52494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38575</t>
+          <t>37773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>65660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72543</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109847</t>
+          <t>110245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317003</t>
+          <t>317470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>340822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320501</t>
+          <t>321623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348708</t>
+          <t>349510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>647400</t>
+          <t>647002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>684704</t>
+          <t>684258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40873</t>
+          <t>40415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>43404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72521</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175941</t>
+          <t>175477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194776</t>
+          <t>193723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177714</t>
+          <t>178172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197458</t>
+          <t>198061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357287</t>
+          <t>359571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386997</t>
+          <t>386404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62071</t>
+          <t>62146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229671</t>
+          <t>228976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247450</t>
+          <t>247378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237080</t>
+          <t>236711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256696</t>
+          <t>257049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474167</t>
+          <t>474092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500527</t>
+          <t>501439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72671</t>
+          <t>69323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87195</t>
+          <t>88604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127701</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>587857</t>
+          <t>589044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>616348</t>
+          <t>618300</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618623</t>
+          <t>621971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650258</t>
+          <t>651898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1220151</t>
+          <t>1219710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1260657</t>
+          <t>1259248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>87933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>72835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112586</t>
+          <t>111153</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133731</t>
+          <t>135914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184748</t>
+          <t>187692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693356</t>
+          <t>690650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724982</t>
+          <t>724192</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>713581</t>
+          <t>715014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>752693</t>
+          <t>753332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1420002</t>
+          <t>1417058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1471019</t>
+          <t>1468836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>288562</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>351265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>355114</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>426247</t>
+          <t>430273</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>655952</t>
+          <t>657075</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>761295</t>
+          <t>762250</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3037814</t>
+          <t>3043085</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3105788</t>
+          <t>3110609</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3118295</t>
+          <t>3114269</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3195707</t>
+          <t>3189428</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6177597</t>
+          <t>6176642</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6282940</t>
+          <t>6281817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>50962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>78369</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>65446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>92693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>273180</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261577</t>
+          <t>267883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282809</t>
+          <t>290297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>251453</t>
+          <t>276257</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242415</t>
+          <t>267273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259670</t>
+          <t>284586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>524632</t>
+          <t>556537</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510646</t>
+          <t>542213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537997</t>
+          <t>569460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,27 +11040,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48798</t>
+          <t>50475</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35901</t>
+          <t>36880</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64451</t>
+          <t>65987</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51465</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>110988</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93256</t>
+          <t>96456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128918</t>
+          <t>137520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -11153,22 +11153,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>468595</t>
+          <t>479185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>452942</t>
+          <t>463673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481492</t>
+          <t>492780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>451535</t>
+          <t>480010</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>438497</t>
+          <t>467138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462260</t>
+          <t>492593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920130</t>
+          <t>959195</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>902200</t>
+          <t>937353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937862</t>
+          <t>978417</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>55764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>102258</t>
+          <t>102671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89179</t>
+          <t>87347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119295</t>
+          <t>117816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>268450</t>
+          <t>269086</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256752</t>
+          <t>256212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279073</t>
+          <t>278947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>294469</t>
+          <t>300617</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283874</t>
+          <t>289272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305174</t>
+          <t>311172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>562920</t>
+          <t>569704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545883</t>
+          <t>554559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575999</t>
+          <t>585028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50067</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>54806</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>45149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68890</t>
+          <t>65885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>82068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109258</t>
+          <t>114340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>275270</t>
+          <t>330994</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262490</t>
+          <t>316579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>285549</t>
+          <t>342044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>424427</t>
+          <t>367155</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>406828</t>
+          <t>356076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>444185</t>
+          <t>376812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>699696</t>
+          <t>698150</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679016</t>
+          <t>680767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724145</t>
+          <t>713039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53253</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75190</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65661</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87110</t>
+          <t>90191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>174208</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140364</t>
+          <t>165836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155695</t>
+          <t>181659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>162695</t>
+          <t>179442</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155403</t>
+          <t>171589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170265</t>
+          <t>186355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>312208</t>
+          <t>353649</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300288</t>
+          <t>342688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321737</t>
+          <t>365245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68449</t>
+          <t>67433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36138</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87196</t>
+          <t>86363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>114363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>213147</t>
+          <t>215292</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201187</t>
+          <t>203274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222532</t>
+          <t>225879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>213616</t>
+          <t>218704</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204654</t>
+          <t>210214</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220918</t>
+          <t>227124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>426762</t>
+          <t>433997</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413589</t>
+          <t>420094</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439496</t>
+          <t>448094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>66470</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>63522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81525</t>
+          <t>98227</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>296202</t>
+          <t>110175</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>93985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>575411</t>
+          <t>128186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>362672</t>
+          <t>188987</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173702</t>
+          <t>167275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>761311</t>
+          <t>213825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>557809</t>
+          <t>640875</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>542754</t>
+          <t>621460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>572076</t>
+          <t>656165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>553063</t>
+          <t>661882</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273854</t>
+          <t>643871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>735455</t>
+          <t>678072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1110872</t>
+          <t>1302757</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>712233</t>
+          <t>1277919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1299842</t>
+          <t>1324469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>71801</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33349</t>
+          <t>66230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103480</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>99758</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72906</t>
+          <t>84535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100757</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>158285</t>
+          <t>179471</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93669</t>
+          <t>159793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192930</t>
+          <t>203894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>856919</t>
+          <t>718359</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>825240</t>
+          <t>700793</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>895371</t>
+          <t>731842</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>628367</t>
+          <t>730248</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>614094</t>
+          <t>714968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641945</t>
+          <t>745471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1485287</t>
+          <t>1448607</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1450642</t>
+          <t>1424184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549903</t>
+          <t>1468285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>294988</t>
+          <t>390015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>442832</t>
+          <t>458262</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>486816</t>
+          <t>486233</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1202240</t>
+          <t>551151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>867714</t>
+          <t>891729</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1724811</t>
+          <t>993896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3062882</t>
+          <t>3108280</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3015988</t>
+          <t>3073513</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3163832</t>
+          <t>3141760</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2979625</t>
+          <t>3214316</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2455793</t>
+          <t>3181494</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3171217</t>
+          <t>3246412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6042507</t>
+          <t>6322595</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5392042</t>
+          <t>6270523</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6249139</t>
+          <t>6372690</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
